--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-09-2025.xlsx
@@ -553,24 +553,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>£10.50</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>£10.68</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>£10.95</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>£11.00</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>£10.90</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>£10.95</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>£11.00</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>£11.17</t>
@@ -588,31 +588,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£16.09</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -674,19 +650,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>£12.05</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>£12.30</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>£12.30</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>£12.50</t>
@@ -709,31 +685,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£18.88</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -795,12 +747,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>£16.50</t>
+          <t>£15.50</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>£15.70</t>
+          <t>£15.39</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -830,31 +782,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£22.31</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -916,24 +844,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>£16.00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>£15.67</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>£15.99</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>£16.50</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>£15.99</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>£15.99</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>£16.50</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>£16.75</t>
@@ -951,31 +879,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£23.71</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1037,12 +941,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£20.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£19.85</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1072,31 +976,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£27.93</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1158,29 +1038,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>£22.50</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>£21.79</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>£22.23</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>£22.62</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>£23.15</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>£22.23</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>£22.23</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>£22.62</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>£23.15</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>£22.24</t>
@@ -1193,31 +1073,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£34.34</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1284,7 +1140,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>£23.60</t>
+          <t>£22.54</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1314,31 +1170,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£35.77</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1400,34 +1232,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£25.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>£25.27</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>£25.79</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>£26.00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>£26.79</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>£25.79</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>£26.00</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>£26.79</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>£25.79</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>£25.27</t>
@@ -1435,31 +1267,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£37.27</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1521,12 +1329,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>£28.80</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>£27.90</t>
+          <t>£27.34</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1556,31 +1364,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£40.61</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1642,12 +1426,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>£28.33</t>
+          <t>£27.00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>£27.95</t>
+          <t>£27.39</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1677,31 +1461,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£42.92</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1763,24 +1523,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>£36.50</t>
+          <t>£36.00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>£35.57</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>£36.30</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>£36.30</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>£36.30</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>£41.79</t>
@@ -1798,31 +1558,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£52.24</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1884,24 +1620,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>£34.50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>£34.10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>£33.99</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>£35.00</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>£34.80</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£33.99</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>£35.00</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>£35.08</t>
@@ -1919,31 +1655,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£52.20</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2005,19 +1717,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>£40.27</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>£41.09</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>£41.09</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>£44.00</t>
@@ -2040,31 +1752,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£60.89</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2126,12 +1814,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>£44.00</t>
+          <t>£41.50</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>£41.90</t>
+          <t>£41.06</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2161,31 +1849,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£65.19</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2247,12 +1911,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>£43.50</t>
+          <t>£41.50</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£41.80</t>
+          <t>£40.96</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2282,31 +1946,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£61.72</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2368,12 +2008,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>£700.00</t>
+          <t>£695.00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>£895.8</t>
+          <t>£877.92</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2465,12 +2105,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>£915.00</t>
+          <t>£895.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>£1189.8</t>
+          <t>£960.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2500,31 +2140,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£1,184.54</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2591,7 +2207,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>£30.50</t>
+          <t>£29.80</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2621,31 +2237,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£47.06</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2712,7 +2304,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>£37.25</t>
+          <t>£36.00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2742,31 +2334,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£55.59</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2833,7 +2401,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>£40.30</t>
+          <t>£39.15</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2863,31 +2431,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£60.48</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2954,7 +2498,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>£46.36</t>
+          <t>£43.62</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2984,31 +2528,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£65.53</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3105,31 +2625,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£67.96</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3226,31 +2722,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£69.12</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3347,31 +2819,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£1235.52</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3468,31 +2916,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.81); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff659d1fc95+79861]
-	GetHandleVerifier [0x0x7ff659d1fcf0+79952]
-	(No symbol) [0x0x7ff659a9cada]
-	(No symbol) [0x0x7ff659af4457]
-	(No symbol) [0x0x7ff659af471c]
-	(No symbol) [0x0x7ff659b48217]
-	(No symbol) [0x0x7ff659b1cb1f]
-	(No symbol) [0x0x7ff659b44f8b]
-	(No symbol) [0x0x7ff659b1c8b3]
-	(No symbol) [0x0x7ff659ae5272]
-	(No symbol) [0x0x7ff659ae6043]
-	GetHandleVerifier [0x0x7ff659fdb9cd+2946349]
-	GetHandleVerifier [0x0x7ff659fd5c4a+2922410]
-	GetHandleVerifier [0x0x7ff659ff59d7+3052855]
-	GetHandleVerifier [0x0x7ff659d3aa7e+189918]
-	GetHandleVerifier [0x0x7ff659d42a1f+222591]
-	GetHandleVerifier [0x0x7ff659d28ab4+116244]
-	GetHandleVerifier [0x0x7ff659d28c69+116681]
-	GetHandleVerifier [0x0x7ff659d0f048+11176]
-	BaseThreadInitThunk [0x0x7ffab550e8d7+23]
-	RtlUserThreadStart [0x0x7ffab5768d9c+44]
-</t>
+          <t>£68.67</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
